--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -883,7 +883,7 @@
         <v>136338282</v>
       </c>
       <c r="B4" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79475</v>
+        <v>79477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33625-2022 artfynd.xlsx
+++ b/artfynd/A 33625-2022 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>136337503</v>
       </c>
       <c r="B5" t="n">
-        <v>79481</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
